--- a/output/tables/main/sm_jct_replication_scenarios.xlsx
+++ b/output/tables/main/sm_jct_replication_scenarios.xlsx
@@ -109,7 +109,7 @@
     <t xml:space="preserve">note</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated 2026-06-09 13:58:21 EDT.</t>
+    <t xml:space="preserve">Generated 2026-06-09 16:49:22 EDT.</t>
   </si>
   <si>
     <t xml:space="preserve">Source: canonical modeled frame data/processed/sipp_modeled.parquet (01b_build_modeled_frame.R).</t>
